--- a/artfynd/A 536-2023 artfynd.xlsx
+++ b/artfynd/A 536-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112168615</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111335715</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111335718</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1101,8 +1121,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112648183</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 536-2023 artfynd.xlsx
+++ b/artfynd/A 536-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,32 +801,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111335715</v>
+        <v>136248749</v>
       </c>
       <c r="B3" t="n">
-        <v>80432</v>
+        <v>80420</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>389</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448695</v>
+        <v>448390</v>
       </c>
       <c r="R3" t="n">
-        <v>7180488</v>
+        <v>7180651</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,9 +883,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -895,44 +914,44 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Martin Westberg, Måns Svensson, Ola Hammarström</t>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111335715</t>
+          <t>https://artportalen.se/Sighting/136248749</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111335718</v>
+        <v>136248998</v>
       </c>
       <c r="B4" t="n">
-        <v>80461</v>
+        <v>78803</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -945,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448695</v>
+        <v>448501</v>
       </c>
       <c r="R4" t="n">
-        <v>7180488</v>
+        <v>7180542</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,12 +994,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,6 +1012,21 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
@@ -1001,22 +1035,22 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Martin Westberg, Måns Svensson, Ola Hammarström</t>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111335718</t>
+          <t>https://artportalen.se/Sighting/136248998</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112648183</v>
+        <v>136248766</v>
       </c>
       <c r="B5" t="n">
-        <v>78390</v>
+        <v>80568</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,21 +1058,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228748</v>
+        <v>1083</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovelmössing</t>
+          <t>Västlig njurlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sclerococcum lobariellum</t>
+          <t>Nephroma laevigatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Diederich</t>
+          <t>Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1047,14 +1081,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2 km NNV Storliden, Lerdalen, biflöde Storlidfjällets sydsluttning, Jmt</t>
+          <t>Lerdalsälven, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448684</v>
+        <v>448390</v>
       </c>
       <c r="R5" t="n">
-        <v>7180467</v>
+        <v>7180651</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,17 +1115,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På lunglav på sälg.</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,26 +1133,5411 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>Uppsala-Evolutionsmuseet</t>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Robin Isaksson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Måns Svensson, Ola Hammarström, Martin Westberg, Robin Isaksson</t>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136248766</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136248747</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79603</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>448390</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7180651</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248747</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136248888</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79603</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>448460</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7180581</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248888</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136249008</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79603</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>448501</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7180542</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136249008</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136248737</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80560</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>448387</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7180665</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248737</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136248746</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80560</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>448390</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7180651</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248746</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136248867</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80560</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>448463</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7180587</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248867</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136248981</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80560</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>448501</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7180542</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248981</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136249063</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80560</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>448523</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7180480</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136249063</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136249001</v>
+      </c>
+      <c r="B14" t="n">
+        <v>75403</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>448501</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7180542</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136249001</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>111335715</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>448695</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7180488</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Martin Westberg, Måns Svensson, Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111335715</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136248732</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80559</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>448387</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7180665</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248732</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136248802</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80559</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>448385</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7180534</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gråal</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Alnus incana</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Alnus incana</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248802</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136248979</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80559</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>448501</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7180542</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248979</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136249015</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80559</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>448499</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7180505</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136249015</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136249059</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80559</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>448523</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7180480</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136249059</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>111335718</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>448695</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7180488</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Martin Westberg, Måns Svensson, Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111335718</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136248769</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80564</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>448390</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7180651</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248769</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136248850</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80570</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>448438</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7180620</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248850</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136248865</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80570</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>448463</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7180587</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248865</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136249041</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80570</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>448521</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7180480</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136249041</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136249066</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80570</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>448523</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7180480</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136249066</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136248882</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80571</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>448463</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7180587</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248882</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136249050</v>
+      </c>
+      <c r="B28" t="n">
+        <v>82359</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>228723</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Protounguicularia nephromatis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Zhurb. &amp; Zavarzin) Huhtinen et al.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>448521</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7180480</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136249050</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>112648183</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78390</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>228748</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Skrovelmössing</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Sclerococcum lobariellum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Nyl.) Ertz &amp; Diederich</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2 km NNV Storliden, Lerdalen, biflöde Storlidfjällets sydsluttning, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>448684</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7180467</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På lunglav på sälg.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Måns Svensson, Ola Hammarström, Martin Westberg, Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/112648183</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136249182</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78504</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>228748</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Skrovelmössing</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Sclerococcum lobariellum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Nyl.) Ertz &amp; Diederich</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>448695</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7180488</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>lunglav</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Salix caprea # lunglav</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136249182</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136249068</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80579</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>229504</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Grynig filtlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Peltigera collina</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>448523</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7180480</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136249068</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>136248786</v>
+      </c>
+      <c r="B32" t="n">
+        <v>81504</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>229558</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Barkporlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Pertusaria sommerfeltii</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Flörke ex Sommerf.) Fr.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>448410</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7180655</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248786</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>136248724</v>
+      </c>
+      <c r="B33" t="n">
+        <v>75460</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>229653</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Njurlavsknapp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Plectocarpon nephromeum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Norman) R.Sant.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>448310</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7180611</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248724</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>136248767</v>
+      </c>
+      <c r="B34" t="n">
+        <v>75460</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>229653</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Njurlavsknapp</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Plectocarpon nephromeum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Norman) R.Sant.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>448390</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7180651</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>stuplav</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia # stuplav</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248767</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>136248848</v>
+      </c>
+      <c r="B35" t="n">
+        <v>75460</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>229653</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Njurlavsknapp</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Plectocarpon nephromeum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Norman) R.Sant.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>448438</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7180620</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248848</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>136249061</v>
+      </c>
+      <c r="B36" t="n">
+        <v>75460</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>229653</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Njurlavsknapp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Plectocarpon nephromeum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Norman) R.Sant.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>448523</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7180480</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136249061</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>136258295</v>
+      </c>
+      <c r="B37" t="n">
+        <v>75460</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>229653</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Njurlavsknapp</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Plectocarpon nephromeum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Norman) R.Sant.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>448338</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7180629</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AL37" t="inlineStr">
+        <is>
+          <t>Nephroma</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia # Nephroma</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136258295</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>136248733</v>
+      </c>
+      <c r="B38" t="n">
+        <v>80515</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>448387</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7180665</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248733</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>136248783</v>
+      </c>
+      <c r="B39" t="n">
+        <v>86773</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>229848</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Refractohilum galligenum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>448390</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7180651</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248783</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>136248878</v>
+      </c>
+      <c r="B40" t="n">
+        <v>86773</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>229848</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Refractohilum galligenum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>448463</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7180587</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>luddlav</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248878</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>136248885</v>
+      </c>
+      <c r="B41" t="n">
+        <v>86773</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>229848</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Refractohilum galligenum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>448460</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7180581</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248885</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>136249039</v>
+      </c>
+      <c r="B42" t="n">
+        <v>86773</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>229848</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Refractohilum galligenum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>448521</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7180480</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136249039</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>136248812</v>
+      </c>
+      <c r="B43" t="n">
+        <v>77073</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6000458</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Abrothallus lobariae</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Diederich &amp; Etayo) Diederich &amp; Ertz</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>448385</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7180534</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gråal</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Alnus incana</t>
+        </is>
+      </c>
+      <c r="AL43" t="inlineStr">
+        <is>
+          <t>lunglav</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Alnus incana # lunglav</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248812</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>136248818</v>
+      </c>
+      <c r="B44" t="n">
+        <v>77073</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6000458</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Abrothallus lobariae</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Diederich &amp; Etayo) Diederich &amp; Ertz</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>448377</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7180557</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gråal</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Alnus incana</t>
+        </is>
+      </c>
+      <c r="AL44" t="inlineStr">
+        <is>
+          <t>lunglav</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Alnus incana # lunglav</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248818</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>136259146</v>
+      </c>
+      <c r="B45" t="n">
+        <v>77073</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6000458</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Abrothallus lobariae</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Diederich &amp; Etayo) Diederich &amp; Ertz</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>448425</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7180600</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gråal</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Alnus incana</t>
+        </is>
+      </c>
+      <c r="AL45" t="inlineStr">
+        <is>
+          <t>lunglav</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Alnus incana # lunglav</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136259146</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>136248826</v>
+      </c>
+      <c r="B46" t="n">
+        <v>82625</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6021661</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Calycina lobariae</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Etayo) Suija &amp; F.Jonss.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>448377</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7180557</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gråal</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Alnus incana</t>
+        </is>
+      </c>
+      <c r="AL46" t="inlineStr">
+        <is>
+          <t>lunglav</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Alnus incana # lunglav</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248826</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>136261692</v>
+      </c>
+      <c r="B47" t="n">
+        <v>85450</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6331313</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Roselliniella nephromatis</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(P.Crouan &amp; H.Crouan) Matzer &amp; Hafellner</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>448499</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7180505</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136261692</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>136248872</v>
+      </c>
+      <c r="B48" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6331317</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Rostania pallida</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>A.Košuth. et al.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>448463</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7180587</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248872</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>136249028</v>
+      </c>
+      <c r="B49" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6331317</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Rostania pallida</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>A.Košuth. et al.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>448521</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7180480</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136249028</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>136258291</v>
+      </c>
+      <c r="B50" t="n">
+        <v>77940</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6332624</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Merismatium lobariae</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Zhurb.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>448338</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7180629</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AL50" t="inlineStr">
+        <is>
+          <t>nephroma</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia # nephroma</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136258291</t>
         </is>
       </c>
     </row>
@@ -1133,6 +6547,51 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 536-2023 artfynd.xlsx
+++ b/artfynd/A 536-2023 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136248749</v>
       </c>
       <c r="B3" t="n">
-        <v>80420</v>
+        <v>80421</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>136248998</v>
       </c>
       <c r="B4" t="n">
-        <v>78803</v>
+        <v>78804</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>136248766</v>
       </c>
       <c r="B5" t="n">
-        <v>80568</v>
+        <v>80569</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>136248747</v>
       </c>
       <c r="B6" t="n">
-        <v>79603</v>
+        <v>79604</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>136248888</v>
       </c>
       <c r="B7" t="n">
-        <v>79603</v>
+        <v>79604</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>136249008</v>
       </c>
       <c r="B8" t="n">
-        <v>79603</v>
+        <v>79604</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>136248737</v>
       </c>
       <c r="B9" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1655,7 +1655,7 @@
         <v>136248746</v>
       </c>
       <c r="B10" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>136248867</v>
       </c>
       <c r="B11" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>136248981</v>
       </c>
       <c r="B12" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136249063</v>
       </c>
       <c r="B13" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136249001</v>
       </c>
       <c r="B14" t="n">
-        <v>75403</v>
+        <v>75404</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>136248732</v>
       </c>
       <c r="B16" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2487,7 +2487,7 @@
         <v>136248802</v>
       </c>
       <c r="B17" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>136248979</v>
       </c>
       <c r="B18" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>136249015</v>
       </c>
       <c r="B19" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>136249059</v>
       </c>
       <c r="B20" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>136248769</v>
       </c>
       <c r="B22" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>136248850</v>
       </c>
       <c r="B23" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>136248865</v>
       </c>
       <c r="B24" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>136249041</v>
       </c>
       <c r="B25" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>136249066</v>
       </c>
       <c r="B26" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         <v>136248882</v>
       </c>
       <c r="B27" t="n">
-        <v>80571</v>
+        <v>80572</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>136249050</v>
       </c>
       <c r="B28" t="n">
-        <v>82359</v>
+        <v>82360</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>136249182</v>
       </c>
       <c r="B30" t="n">
-        <v>78504</v>
+        <v>78505</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>136249068</v>
       </c>
       <c r="B31" t="n">
-        <v>80579</v>
+        <v>80580</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>136248786</v>
       </c>
       <c r="B32" t="n">
-        <v>81504</v>
+        <v>81505</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>136248724</v>
       </c>
       <c r="B33" t="n">
-        <v>75460</v>
+        <v>75461</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>136248767</v>
       </c>
       <c r="B34" t="n">
-        <v>75460</v>
+        <v>75461</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>136248848</v>
       </c>
       <c r="B35" t="n">
-        <v>75460</v>
+        <v>75461</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>136249061</v>
       </c>
       <c r="B36" t="n">
-        <v>75460</v>
+        <v>75461</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         <v>136258295</v>
       </c>
       <c r="B37" t="n">
-        <v>75460</v>
+        <v>75461</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>136248733</v>
       </c>
       <c r="B38" t="n">
-        <v>80515</v>
+        <v>80516</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5128,7 +5128,7 @@
         <v>136248783</v>
       </c>
       <c r="B39" t="n">
-        <v>86773</v>
+        <v>86774</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>136248878</v>
       </c>
       <c r="B40" t="n">
-        <v>86773</v>
+        <v>86774</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>136248885</v>
       </c>
       <c r="B41" t="n">
-        <v>86773</v>
+        <v>86774</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>136249039</v>
       </c>
       <c r="B42" t="n">
-        <v>86773</v>
+        <v>86774</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>136248812</v>
       </c>
       <c r="B43" t="n">
-        <v>77073</v>
+        <v>77074</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>136248818</v>
       </c>
       <c r="B44" t="n">
-        <v>77073</v>
+        <v>77074</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>136259146</v>
       </c>
       <c r="B45" t="n">
-        <v>77073</v>
+        <v>77074</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>136248826</v>
       </c>
       <c r="B46" t="n">
-        <v>82625</v>
+        <v>82626</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>136261692</v>
       </c>
       <c r="B47" t="n">
-        <v>85450</v>
+        <v>85451</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
         <v>136248872</v>
       </c>
       <c r="B48" t="n">
-        <v>80461</v>
+        <v>80462</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>136249028</v>
       </c>
       <c r="B49" t="n">
-        <v>80461</v>
+        <v>80462</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>136258291</v>
       </c>
       <c r="B50" t="n">
-        <v>77940</v>
+        <v>77941</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 536-2023 artfynd.xlsx
+++ b/artfynd/A 536-2023 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136248749</v>
       </c>
       <c r="B3" t="n">
-        <v>80421</v>
+        <v>80425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>136248998</v>
       </c>
       <c r="B4" t="n">
-        <v>78804</v>
+        <v>78808</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>136248766</v>
       </c>
       <c r="B5" t="n">
-        <v>80569</v>
+        <v>80573</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>136248747</v>
       </c>
       <c r="B6" t="n">
-        <v>79604</v>
+        <v>79608</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>136248888</v>
       </c>
       <c r="B7" t="n">
-        <v>79604</v>
+        <v>79608</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>136249008</v>
       </c>
       <c r="B8" t="n">
-        <v>79604</v>
+        <v>79608</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>136248737</v>
       </c>
       <c r="B9" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1655,7 +1655,7 @@
         <v>136248746</v>
       </c>
       <c r="B10" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>136248867</v>
       </c>
       <c r="B11" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>136248981</v>
       </c>
       <c r="B12" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136249063</v>
       </c>
       <c r="B13" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136249001</v>
       </c>
       <c r="B14" t="n">
-        <v>75404</v>
+        <v>75408</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>136248732</v>
       </c>
       <c r="B16" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2487,7 +2487,7 @@
         <v>136248802</v>
       </c>
       <c r="B17" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>136248979</v>
       </c>
       <c r="B18" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>136249015</v>
       </c>
       <c r="B19" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>136249059</v>
       </c>
       <c r="B20" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>136248769</v>
       </c>
       <c r="B22" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>136248850</v>
       </c>
       <c r="B23" t="n">
-        <v>80571</v>
+        <v>80575</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>136248865</v>
       </c>
       <c r="B24" t="n">
-        <v>80571</v>
+        <v>80575</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>136249041</v>
       </c>
       <c r="B25" t="n">
-        <v>80571</v>
+        <v>80575</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>136249066</v>
       </c>
       <c r="B26" t="n">
-        <v>80571</v>
+        <v>80575</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         <v>136248882</v>
       </c>
       <c r="B27" t="n">
-        <v>80572</v>
+        <v>80576</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>136249050</v>
       </c>
       <c r="B28" t="n">
-        <v>82360</v>
+        <v>82364</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>136249182</v>
       </c>
       <c r="B30" t="n">
-        <v>78505</v>
+        <v>78509</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>136249068</v>
       </c>
       <c r="B31" t="n">
-        <v>80580</v>
+        <v>80584</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>136248786</v>
       </c>
       <c r="B32" t="n">
-        <v>81505</v>
+        <v>81509</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>136248724</v>
       </c>
       <c r="B33" t="n">
-        <v>75461</v>
+        <v>75465</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>136248767</v>
       </c>
       <c r="B34" t="n">
-        <v>75461</v>
+        <v>75465</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>136248848</v>
       </c>
       <c r="B35" t="n">
-        <v>75461</v>
+        <v>75465</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>136249061</v>
       </c>
       <c r="B36" t="n">
-        <v>75461</v>
+        <v>75465</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         <v>136258295</v>
       </c>
       <c r="B37" t="n">
-        <v>75461</v>
+        <v>75465</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>136248733</v>
       </c>
       <c r="B38" t="n">
-        <v>80516</v>
+        <v>80520</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5128,7 +5128,7 @@
         <v>136248783</v>
       </c>
       <c r="B39" t="n">
-        <v>86774</v>
+        <v>86780</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>136248878</v>
       </c>
       <c r="B40" t="n">
-        <v>86774</v>
+        <v>86780</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>136248885</v>
       </c>
       <c r="B41" t="n">
-        <v>86774</v>
+        <v>86780</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>136249039</v>
       </c>
       <c r="B42" t="n">
-        <v>86774</v>
+        <v>86780</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>136248812</v>
       </c>
       <c r="B43" t="n">
-        <v>77074</v>
+        <v>77078</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>136248818</v>
       </c>
       <c r="B44" t="n">
-        <v>77074</v>
+        <v>77078</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>136259146</v>
       </c>
       <c r="B45" t="n">
-        <v>77074</v>
+        <v>77078</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>136248826</v>
       </c>
       <c r="B46" t="n">
-        <v>82626</v>
+        <v>82630</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>136261692</v>
       </c>
       <c r="B47" t="n">
-        <v>85451</v>
+        <v>85455</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
         <v>136248872</v>
       </c>
       <c r="B48" t="n">
-        <v>80462</v>
+        <v>80466</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>136249028</v>
       </c>
       <c r="B49" t="n">
-        <v>80462</v>
+        <v>80466</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>136258291</v>
       </c>
       <c r="B50" t="n">
-        <v>77941</v>
+        <v>77945</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 536-2023 artfynd.xlsx
+++ b/artfynd/A 536-2023 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136248749</v>
       </c>
       <c r="B3" t="n">
-        <v>80425</v>
+        <v>80426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>136248998</v>
       </c>
       <c r="B4" t="n">
-        <v>78808</v>
+        <v>78809</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>136248766</v>
       </c>
       <c r="B5" t="n">
-        <v>80573</v>
+        <v>80574</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>136248747</v>
       </c>
       <c r="B6" t="n">
-        <v>79608</v>
+        <v>79609</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>136248888</v>
       </c>
       <c r="B7" t="n">
-        <v>79608</v>
+        <v>79609</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>136249008</v>
       </c>
       <c r="B8" t="n">
-        <v>79608</v>
+        <v>79609</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>136248737</v>
       </c>
       <c r="B9" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>136248746</v>
       </c>
       <c r="B10" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>136248867</v>
       </c>
       <c r="B11" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>136248981</v>
       </c>
       <c r="B12" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136249063</v>
       </c>
       <c r="B13" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136249001</v>
       </c>
       <c r="B14" t="n">
-        <v>75408</v>
+        <v>75409</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>136248732</v>
       </c>
       <c r="B16" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>136248802</v>
       </c>
       <c r="B17" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>136248979</v>
       </c>
       <c r="B18" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>136249015</v>
       </c>
       <c r="B19" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>136249059</v>
       </c>
       <c r="B20" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>136248769</v>
       </c>
       <c r="B22" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>136248850</v>
       </c>
       <c r="B23" t="n">
-        <v>80575</v>
+        <v>80576</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>136248865</v>
       </c>
       <c r="B24" t="n">
-        <v>80575</v>
+        <v>80576</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>136249041</v>
       </c>
       <c r="B25" t="n">
-        <v>80575</v>
+        <v>80576</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>136249066</v>
       </c>
       <c r="B26" t="n">
-        <v>80575</v>
+        <v>80576</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         <v>136248882</v>
       </c>
       <c r="B27" t="n">
-        <v>80576</v>
+        <v>80577</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>136249050</v>
       </c>
       <c r="B28" t="n">
-        <v>82364</v>
+        <v>82365</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>136249182</v>
       </c>
       <c r="B30" t="n">
-        <v>78509</v>
+        <v>78510</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>136249068</v>
       </c>
       <c r="B31" t="n">
-        <v>80584</v>
+        <v>80585</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>136248786</v>
       </c>
       <c r="B32" t="n">
-        <v>81509</v>
+        <v>81510</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>136248724</v>
       </c>
       <c r="B33" t="n">
-        <v>75465</v>
+        <v>75466</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>136248767</v>
       </c>
       <c r="B34" t="n">
-        <v>75465</v>
+        <v>75466</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>136248848</v>
       </c>
       <c r="B35" t="n">
-        <v>75465</v>
+        <v>75466</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>136249061</v>
       </c>
       <c r="B36" t="n">
-        <v>75465</v>
+        <v>75466</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         <v>136258295</v>
       </c>
       <c r="B37" t="n">
-        <v>75465</v>
+        <v>75466</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>136248733</v>
       </c>
       <c r="B38" t="n">
-        <v>80520</v>
+        <v>80521</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>136248783</v>
       </c>
       <c r="B39" t="n">
-        <v>86780</v>
+        <v>86781</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>136248878</v>
       </c>
       <c r="B40" t="n">
-        <v>86780</v>
+        <v>86781</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>136248885</v>
       </c>
       <c r="B41" t="n">
-        <v>86780</v>
+        <v>86781</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>136249039</v>
       </c>
       <c r="B42" t="n">
-        <v>86780</v>
+        <v>86781</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>136248812</v>
       </c>
       <c r="B43" t="n">
-        <v>77078</v>
+        <v>77079</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>136248818</v>
       </c>
       <c r="B44" t="n">
-        <v>77078</v>
+        <v>77079</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>136259146</v>
       </c>
       <c r="B45" t="n">
-        <v>77078</v>
+        <v>77079</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>136248826</v>
       </c>
       <c r="B46" t="n">
-        <v>82630</v>
+        <v>82631</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>136261692</v>
       </c>
       <c r="B47" t="n">
-        <v>85455</v>
+        <v>85456</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
         <v>136248872</v>
       </c>
       <c r="B48" t="n">
-        <v>80466</v>
+        <v>80467</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>136249028</v>
       </c>
       <c r="B49" t="n">
-        <v>80466</v>
+        <v>80467</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>136258291</v>
       </c>
       <c r="B50" t="n">
-        <v>77945</v>
+        <v>77946</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 536-2023 artfynd.xlsx
+++ b/artfynd/A 536-2023 artfynd.xlsx
@@ -5592,7 +5592,7 @@
         <v>136248812</v>
       </c>
       <c r="B43" t="n">
-        <v>77079</v>
+        <v>77083</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 536-2023 artfynd.xlsx
+++ b/artfynd/A 536-2023 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136248749</v>
       </c>
       <c r="B3" t="n">
-        <v>80426</v>
+        <v>80430</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>136248998</v>
       </c>
       <c r="B4" t="n">
-        <v>78809</v>
+        <v>78813</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>136248766</v>
       </c>
       <c r="B5" t="n">
-        <v>80574</v>
+        <v>80578</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>136248747</v>
       </c>
       <c r="B6" t="n">
-        <v>79609</v>
+        <v>79613</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>136248888</v>
       </c>
       <c r="B7" t="n">
-        <v>79609</v>
+        <v>79613</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>136249008</v>
       </c>
       <c r="B8" t="n">
-        <v>79609</v>
+        <v>79613</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>136248737</v>
       </c>
       <c r="B9" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>136248746</v>
       </c>
       <c r="B10" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>136248867</v>
       </c>
       <c r="B11" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>136248981</v>
       </c>
       <c r="B12" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136249063</v>
       </c>
       <c r="B13" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136249001</v>
       </c>
       <c r="B14" t="n">
-        <v>75409</v>
+        <v>75413</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>136248732</v>
       </c>
       <c r="B16" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>136248802</v>
       </c>
       <c r="B17" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>136248979</v>
       </c>
       <c r="B18" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>136249015</v>
       </c>
       <c r="B19" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>136249059</v>
       </c>
       <c r="B20" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>136248769</v>
       </c>
       <c r="B22" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>136248850</v>
       </c>
       <c r="B23" t="n">
-        <v>80576</v>
+        <v>80580</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>136248865</v>
       </c>
       <c r="B24" t="n">
-        <v>80576</v>
+        <v>80580</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>136249041</v>
       </c>
       <c r="B25" t="n">
-        <v>80576</v>
+        <v>80580</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>136249066</v>
       </c>
       <c r="B26" t="n">
-        <v>80576</v>
+        <v>80580</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         <v>136248882</v>
       </c>
       <c r="B27" t="n">
-        <v>80577</v>
+        <v>80581</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>136249050</v>
       </c>
       <c r="B28" t="n">
-        <v>82365</v>
+        <v>82369</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>136249182</v>
       </c>
       <c r="B30" t="n">
-        <v>78510</v>
+        <v>78514</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>136249068</v>
       </c>
       <c r="B31" t="n">
-        <v>80585</v>
+        <v>80589</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>136248786</v>
       </c>
       <c r="B32" t="n">
-        <v>81510</v>
+        <v>81514</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>136248724</v>
       </c>
       <c r="B33" t="n">
-        <v>75466</v>
+        <v>75470</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>136248767</v>
       </c>
       <c r="B34" t="n">
-        <v>75466</v>
+        <v>75470</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>136248848</v>
       </c>
       <c r="B35" t="n">
-        <v>75466</v>
+        <v>75470</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>136249061</v>
       </c>
       <c r="B36" t="n">
-        <v>75466</v>
+        <v>75470</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         <v>136258295</v>
       </c>
       <c r="B37" t="n">
-        <v>75466</v>
+        <v>75470</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>136248733</v>
       </c>
       <c r="B38" t="n">
-        <v>80521</v>
+        <v>80525</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>136248783</v>
       </c>
       <c r="B39" t="n">
-        <v>86781</v>
+        <v>86787</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>136248878</v>
       </c>
       <c r="B40" t="n">
-        <v>86781</v>
+        <v>86787</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>136248885</v>
       </c>
       <c r="B41" t="n">
-        <v>86781</v>
+        <v>86787</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>136249039</v>
       </c>
       <c r="B42" t="n">
-        <v>86781</v>
+        <v>86787</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>136248818</v>
       </c>
       <c r="B44" t="n">
-        <v>77079</v>
+        <v>77083</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>136259146</v>
       </c>
       <c r="B45" t="n">
-        <v>77079</v>
+        <v>77083</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>136248826</v>
       </c>
       <c r="B46" t="n">
-        <v>82631</v>
+        <v>82635</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>136261692</v>
       </c>
       <c r="B47" t="n">
-        <v>85456</v>
+        <v>85460</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
         <v>136248872</v>
       </c>
       <c r="B48" t="n">
-        <v>80467</v>
+        <v>80471</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>136249028</v>
       </c>
       <c r="B49" t="n">
-        <v>80467</v>
+        <v>80471</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>136258291</v>
       </c>
       <c r="B50" t="n">
-        <v>77946</v>
+        <v>77950</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 536-2023 artfynd.xlsx
+++ b/artfynd/A 536-2023 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136248749</v>
       </c>
       <c r="B3" t="n">
-        <v>80430</v>
+        <v>80436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>136248998</v>
       </c>
       <c r="B4" t="n">
-        <v>78813</v>
+        <v>78819</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>136248766</v>
       </c>
       <c r="B5" t="n">
-        <v>80578</v>
+        <v>80584</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>136248747</v>
       </c>
       <c r="B6" t="n">
-        <v>79613</v>
+        <v>79619</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>136248888</v>
       </c>
       <c r="B7" t="n">
-        <v>79613</v>
+        <v>79619</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>136249008</v>
       </c>
       <c r="B8" t="n">
-        <v>79613</v>
+        <v>79619</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>136248737</v>
       </c>
       <c r="B9" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>136248746</v>
       </c>
       <c r="B10" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>136248867</v>
       </c>
       <c r="B11" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>136248981</v>
       </c>
       <c r="B12" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136249063</v>
       </c>
       <c r="B13" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136249001</v>
       </c>
       <c r="B14" t="n">
-        <v>75413</v>
+        <v>75419</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>136248732</v>
       </c>
       <c r="B16" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>136248802</v>
       </c>
       <c r="B17" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>136248979</v>
       </c>
       <c r="B18" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>136249015</v>
       </c>
       <c r="B19" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>136249059</v>
       </c>
       <c r="B20" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>136248769</v>
       </c>
       <c r="B22" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>136248850</v>
       </c>
       <c r="B23" t="n">
-        <v>80580</v>
+        <v>80586</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>136248865</v>
       </c>
       <c r="B24" t="n">
-        <v>80580</v>
+        <v>80586</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>136249041</v>
       </c>
       <c r="B25" t="n">
-        <v>80580</v>
+        <v>80586</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>136249066</v>
       </c>
       <c r="B26" t="n">
-        <v>80580</v>
+        <v>80586</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         <v>136248882</v>
       </c>
       <c r="B27" t="n">
-        <v>80581</v>
+        <v>80587</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>136249050</v>
       </c>
       <c r="B28" t="n">
-        <v>82369</v>
+        <v>82375</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>136249182</v>
       </c>
       <c r="B30" t="n">
-        <v>78514</v>
+        <v>78520</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>136249068</v>
       </c>
       <c r="B31" t="n">
-        <v>80589</v>
+        <v>80595</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>136248786</v>
       </c>
       <c r="B32" t="n">
-        <v>81514</v>
+        <v>81520</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>136248724</v>
       </c>
       <c r="B33" t="n">
-        <v>75470</v>
+        <v>75476</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>136248767</v>
       </c>
       <c r="B34" t="n">
-        <v>75470</v>
+        <v>75476</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>136248848</v>
       </c>
       <c r="B35" t="n">
-        <v>75470</v>
+        <v>75476</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>136249061</v>
       </c>
       <c r="B36" t="n">
-        <v>75470</v>
+        <v>75476</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         <v>136258295</v>
       </c>
       <c r="B37" t="n">
-        <v>75470</v>
+        <v>75476</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>136248733</v>
       </c>
       <c r="B38" t="n">
-        <v>80525</v>
+        <v>80531</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>136248783</v>
       </c>
       <c r="B39" t="n">
-        <v>86787</v>
+        <v>86794</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>136248878</v>
       </c>
       <c r="B40" t="n">
-        <v>86787</v>
+        <v>86794</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>136248885</v>
       </c>
       <c r="B41" t="n">
-        <v>86787</v>
+        <v>86794</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>136249039</v>
       </c>
       <c r="B42" t="n">
-        <v>86787</v>
+        <v>86794</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>136248812</v>
       </c>
       <c r="B43" t="n">
-        <v>77083</v>
+        <v>77089</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>136248818</v>
       </c>
       <c r="B44" t="n">
-        <v>77083</v>
+        <v>77089</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>136259146</v>
       </c>
       <c r="B45" t="n">
-        <v>77083</v>
+        <v>77089</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>136248826</v>
       </c>
       <c r="B46" t="n">
-        <v>82635</v>
+        <v>82641</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>136261692</v>
       </c>
       <c r="B47" t="n">
-        <v>85460</v>
+        <v>85467</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
         <v>136248872</v>
       </c>
       <c r="B48" t="n">
-        <v>80471</v>
+        <v>80477</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>136249028</v>
       </c>
       <c r="B49" t="n">
-        <v>80471</v>
+        <v>80477</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>136258291</v>
       </c>
       <c r="B50" t="n">
-        <v>77950</v>
+        <v>77956</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 536-2023 artfynd.xlsx
+++ b/artfynd/A 536-2023 artfynd.xlsx
@@ -2124,7 +2124,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>

--- a/artfynd/A 536-2023 artfynd.xlsx
+++ b/artfynd/A 536-2023 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136248749</v>
       </c>
       <c r="B3" t="n">
-        <v>80436</v>
+        <v>80449</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>136248998</v>
       </c>
       <c r="B4" t="n">
-        <v>78819</v>
+        <v>78832</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>136248766</v>
       </c>
       <c r="B5" t="n">
-        <v>80584</v>
+        <v>80597</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>136248747</v>
       </c>
       <c r="B6" t="n">
-        <v>79619</v>
+        <v>79632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>136248888</v>
       </c>
       <c r="B7" t="n">
-        <v>79619</v>
+        <v>79632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>136249008</v>
       </c>
       <c r="B8" t="n">
-        <v>79619</v>
+        <v>79632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>136248737</v>
       </c>
       <c r="B9" t="n">
-        <v>80576</v>
+        <v>80589</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>136248746</v>
       </c>
       <c r="B10" t="n">
-        <v>80576</v>
+        <v>80589</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>136248867</v>
       </c>
       <c r="B11" t="n">
-        <v>80576</v>
+        <v>80589</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>136248981</v>
       </c>
       <c r="B12" t="n">
-        <v>80576</v>
+        <v>80589</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136249063</v>
       </c>
       <c r="B13" t="n">
-        <v>80576</v>
+        <v>80589</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2139,7 +2139,7 @@
         <v>136249001</v>
       </c>
       <c r="B14" t="n">
-        <v>75419</v>
+        <v>75432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>136248732</v>
       </c>
       <c r="B16" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>136248802</v>
       </c>
       <c r="B17" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>136248979</v>
       </c>
       <c r="B18" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>136249015</v>
       </c>
       <c r="B19" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>136249059</v>
       </c>
       <c r="B20" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3077,7 +3077,7 @@
         <v>136248769</v>
       </c>
       <c r="B22" t="n">
-        <v>80580</v>
+        <v>80593</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>136248850</v>
       </c>
       <c r="B23" t="n">
-        <v>80586</v>
+        <v>80599</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>136248865</v>
       </c>
       <c r="B24" t="n">
-        <v>80586</v>
+        <v>80599</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>136249041</v>
       </c>
       <c r="B25" t="n">
-        <v>80586</v>
+        <v>80599</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3546,7 +3546,7 @@
         <v>136249066</v>
       </c>
       <c r="B26" t="n">
-        <v>80586</v>
+        <v>80599</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         <v>136248882</v>
       </c>
       <c r="B27" t="n">
-        <v>80587</v>
+        <v>80600</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>136249050</v>
       </c>
       <c r="B28" t="n">
-        <v>82375</v>
+        <v>82388</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4020,7 +4020,7 @@
         <v>136249182</v>
       </c>
       <c r="B30" t="n">
-        <v>78520</v>
+        <v>78533</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>136249068</v>
       </c>
       <c r="B31" t="n">
-        <v>80595</v>
+        <v>80608</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>136248786</v>
       </c>
       <c r="B32" t="n">
-        <v>81520</v>
+        <v>81533</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>136248724</v>
       </c>
       <c r="B33" t="n">
-        <v>75476</v>
+        <v>75489</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>136248767</v>
       </c>
       <c r="B34" t="n">
-        <v>75476</v>
+        <v>75489</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>136248848</v>
       </c>
       <c r="B35" t="n">
-        <v>75476</v>
+        <v>75489</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>136249061</v>
       </c>
       <c r="B36" t="n">
-        <v>75476</v>
+        <v>75489</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4877,7 +4877,7 @@
         <v>136258295</v>
       </c>
       <c r="B37" t="n">
-        <v>75476</v>
+        <v>75489</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>136248733</v>
       </c>
       <c r="B38" t="n">
-        <v>80531</v>
+        <v>80544</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>136248783</v>
       </c>
       <c r="B39" t="n">
-        <v>86794</v>
+        <v>86807</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>136248878</v>
       </c>
       <c r="B40" t="n">
-        <v>86794</v>
+        <v>86807</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>136248885</v>
       </c>
       <c r="B41" t="n">
-        <v>86794</v>
+        <v>86807</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>136249039</v>
       </c>
       <c r="B42" t="n">
-        <v>86794</v>
+        <v>86807</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>136248812</v>
       </c>
       <c r="B43" t="n">
-        <v>77089</v>
+        <v>77102</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>136248818</v>
       </c>
       <c r="B44" t="n">
-        <v>77089</v>
+        <v>77102</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>136259146</v>
       </c>
       <c r="B45" t="n">
-        <v>77089</v>
+        <v>77102</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>136248826</v>
       </c>
       <c r="B46" t="n">
-        <v>82641</v>
+        <v>82654</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>136261692</v>
       </c>
       <c r="B47" t="n">
-        <v>85467</v>
+        <v>85480</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
         <v>136248872</v>
       </c>
       <c r="B48" t="n">
-        <v>80477</v>
+        <v>80490</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>136249028</v>
       </c>
       <c r="B49" t="n">
-        <v>80477</v>
+        <v>80490</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>136258291</v>
       </c>
       <c r="B50" t="n">
-        <v>77956</v>
+        <v>77969</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 536-2023 artfynd.xlsx
+++ b/artfynd/A 536-2023 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136248749</v>
       </c>
       <c r="B3" t="n">
-        <v>80449</v>
+        <v>80450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>136248998</v>
       </c>
       <c r="B4" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>136248766</v>
       </c>
       <c r="B5" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>136248747</v>
       </c>
       <c r="B6" t="n">
-        <v>79632</v>
+        <v>79633</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>136248888</v>
       </c>
       <c r="B7" t="n">
-        <v>79632</v>
+        <v>79633</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>136249008</v>
       </c>
       <c r="B8" t="n">
-        <v>79632</v>
+        <v>79633</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>136248737</v>
       </c>
       <c r="B9" t="n">
-        <v>80589</v>
+        <v>80590</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>136248746</v>
       </c>
       <c r="B10" t="n">
-        <v>80589</v>
+        <v>80590</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>136248867</v>
       </c>
       <c r="B11" t="n">
-        <v>80589</v>
+        <v>80590</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>136248981</v>
       </c>
       <c r="B12" t="n">
-        <v>80589</v>
+        <v>80590</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136249063</v>
       </c>
       <c r="B13" t="n">
-        <v>80589</v>
+        <v>80590</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136249001</v>
       </c>
       <c r="B14" t="n">
-        <v>75432</v>
+        <v>75433</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>136248732</v>
       </c>
       <c r="B16" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>136248802</v>
       </c>
       <c r="B17" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>136248979</v>
       </c>
       <c r="B18" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>136249015</v>
       </c>
       <c r="B19" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>136249059</v>
       </c>
       <c r="B20" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>136248769</v>
       </c>
       <c r="B22" t="n">
-        <v>80593</v>
+        <v>80594</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>136248850</v>
       </c>
       <c r="B23" t="n">
-        <v>80599</v>
+        <v>80600</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>136248865</v>
       </c>
       <c r="B24" t="n">
-        <v>80599</v>
+        <v>80600</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>136249041</v>
       </c>
       <c r="B25" t="n">
-        <v>80599</v>
+        <v>80600</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>136249066</v>
       </c>
       <c r="B26" t="n">
-        <v>80599</v>
+        <v>80600</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         <v>136248882</v>
       </c>
       <c r="B27" t="n">
-        <v>80600</v>
+        <v>80601</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>136249050</v>
       </c>
       <c r="B28" t="n">
-        <v>82388</v>
+        <v>82389</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>136249182</v>
       </c>
       <c r="B30" t="n">
-        <v>78533</v>
+        <v>78534</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>136249068</v>
       </c>
       <c r="B31" t="n">
-        <v>80608</v>
+        <v>80609</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>136248786</v>
       </c>
       <c r="B32" t="n">
-        <v>81533</v>
+        <v>81534</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>136248724</v>
       </c>
       <c r="B33" t="n">
-        <v>75489</v>
+        <v>75490</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>136248767</v>
       </c>
       <c r="B34" t="n">
-        <v>75489</v>
+        <v>75490</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>136248848</v>
       </c>
       <c r="B35" t="n">
-        <v>75489</v>
+        <v>75490</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>136249061</v>
       </c>
       <c r="B36" t="n">
-        <v>75489</v>
+        <v>75490</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         <v>136258295</v>
       </c>
       <c r="B37" t="n">
-        <v>75489</v>
+        <v>75490</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>136248733</v>
       </c>
       <c r="B38" t="n">
-        <v>80544</v>
+        <v>80545</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>136248783</v>
       </c>
       <c r="B39" t="n">
-        <v>86807</v>
+        <v>86808</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>136248878</v>
       </c>
       <c r="B40" t="n">
-        <v>86807</v>
+        <v>86808</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>136248885</v>
       </c>
       <c r="B41" t="n">
-        <v>86807</v>
+        <v>86808</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>136249039</v>
       </c>
       <c r="B42" t="n">
-        <v>86807</v>
+        <v>86808</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>136248812</v>
       </c>
       <c r="B43" t="n">
-        <v>77102</v>
+        <v>77103</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>136248818</v>
       </c>
       <c r="B44" t="n">
-        <v>77102</v>
+        <v>77103</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>136259146</v>
       </c>
       <c r="B45" t="n">
-        <v>77102</v>
+        <v>77103</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>136248826</v>
       </c>
       <c r="B46" t="n">
-        <v>82654</v>
+        <v>82655</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>136261692</v>
       </c>
       <c r="B47" t="n">
-        <v>85480</v>
+        <v>85481</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
         <v>136248872</v>
       </c>
       <c r="B48" t="n">
-        <v>80490</v>
+        <v>80491</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>136249028</v>
       </c>
       <c r="B49" t="n">
-        <v>80490</v>
+        <v>80491</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>136258291</v>
       </c>
       <c r="B50" t="n">
-        <v>77969</v>
+        <v>77970</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
